--- a/sulamericana/datasets_sula/2_resultados_quartas_sula.xlsx
+++ b/sulamericana/datasets_sula/2_resultados_quartas_sula.xlsx
@@ -7,8 +7,8 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Rodada 34" sheetId="1" r:id="rId1"/>
-    <sheet name="Rodada 35" sheetId="2" r:id="rId2"/>
+    <sheet name="Rodada 15" sheetId="1" r:id="rId1"/>
+    <sheet name="Rodada 16" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -454,13 +454,19 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
         <v>10</v>
       </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
       <c r="E2" t="s">
         <v>14</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -468,13 +474,19 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
         <v>11</v>
       </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
       <c r="E3" t="s">
         <v>15</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -482,13 +494,19 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
         <v>12</v>
       </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
       <c r="E4" t="s">
         <v>16</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -496,13 +514,19 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
         <v>13</v>
       </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
       <c r="E5" t="s">
         <v>17</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -540,13 +564,19 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
         <v>14</v>
       </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
       <c r="E2" t="s">
         <v>10</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -554,13 +584,19 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
         <v>15</v>
       </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
       <c r="E3" t="s">
         <v>11</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -568,13 +604,19 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
         <v>16</v>
       </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
       <c r="E4" t="s">
         <v>12</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -582,13 +624,19 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
       </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
       <c r="E5" t="s">
         <v>13</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/sulamericana/datasets_sula/2_resultados_quartas_sula.xlsx
+++ b/sulamericana/datasets_sula/2_resultados_quartas_sula.xlsx
@@ -460,13 +460,13 @@
         <v>10</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>55.05</v>
       </c>
       <c r="E2" t="s">
         <v>14</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>37.83</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -480,13 +480,13 @@
         <v>11</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>55.9</v>
       </c>
       <c r="E3" t="s">
         <v>15</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>55.9</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -500,13 +500,13 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>43.73</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>43.82</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -520,13 +520,13 @@
         <v>13</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>67.55</v>
       </c>
       <c r="E5" t="s">
         <v>17</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>68.34999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -569,14 +569,8 @@
       <c r="C2" t="s">
         <v>14</v>
       </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
       <c r="E2" t="s">
         <v>10</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -589,14 +583,8 @@
       <c r="C3" t="s">
         <v>15</v>
       </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
       <c r="E3" t="s">
         <v>11</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -609,14 +597,8 @@
       <c r="C4" t="s">
         <v>16</v>
       </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
       <c r="E4" t="s">
         <v>12</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -629,14 +611,8 @@
       <c r="C5" t="s">
         <v>17</v>
       </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
       <c r="E5" t="s">
         <v>13</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/sulamericana/datasets_sula/2_resultados_quartas_sula.xlsx
+++ b/sulamericana/datasets_sula/2_resultados_quartas_sula.xlsx
@@ -460,13 +460,13 @@
         <v>10</v>
       </c>
       <c r="D2">
-        <v>55.05</v>
+        <v>55.050048828125</v>
       </c>
       <c r="E2" t="s">
         <v>14</v>
       </c>
       <c r="F2">
-        <v>37.83</v>
+        <v>37.830078125</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -480,13 +480,13 @@
         <v>11</v>
       </c>
       <c r="D3">
-        <v>55.9</v>
+        <v>55.89990234375</v>
       </c>
       <c r="E3" t="s">
         <v>15</v>
       </c>
       <c r="F3">
-        <v>55.9</v>
+        <v>55.89990234375</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -500,13 +500,13 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>43.73</v>
+        <v>43.72998046875</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
       </c>
       <c r="F4">
-        <v>43.82</v>
+        <v>43.820068359375</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -520,13 +520,13 @@
         <v>13</v>
       </c>
       <c r="D5">
-        <v>67.55</v>
+        <v>67.5498046875</v>
       </c>
       <c r="E5" t="s">
         <v>17</v>
       </c>
       <c r="F5">
-        <v>68.34999999999999</v>
+        <v>68.35009765625</v>
       </c>
     </row>
   </sheetData>

--- a/sulamericana/datasets_sula/2_resultados_quartas_sula.xlsx
+++ b/sulamericana/datasets_sula/2_resultados_quartas_sula.xlsx
@@ -569,8 +569,14 @@
       <c r="C2" t="s">
         <v>14</v>
       </c>
+      <c r="D2">
+        <v>56.93</v>
+      </c>
       <c r="E2" t="s">
         <v>10</v>
+      </c>
+      <c r="F2">
+        <v>75.88</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -583,8 +589,14 @@
       <c r="C3" t="s">
         <v>15</v>
       </c>
+      <c r="D3">
+        <v>103.39</v>
+      </c>
       <c r="E3" t="s">
         <v>11</v>
+      </c>
+      <c r="F3">
+        <v>82.25</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -597,8 +609,14 @@
       <c r="C4" t="s">
         <v>16</v>
       </c>
+      <c r="D4">
+        <v>59.61</v>
+      </c>
       <c r="E4" t="s">
         <v>12</v>
+      </c>
+      <c r="F4">
+        <v>66.58</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -611,8 +629,14 @@
       <c r="C5" t="s">
         <v>17</v>
       </c>
+      <c r="D5">
+        <v>74.28</v>
+      </c>
       <c r="E5" t="s">
         <v>13</v>
+      </c>
+      <c r="F5">
+        <v>88.68000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/sulamericana/datasets_sula/2_resultados_quartas_sula.xlsx
+++ b/sulamericana/datasets_sula/2_resultados_quartas_sula.xlsx
@@ -570,13 +570,13 @@
         <v>14</v>
       </c>
       <c r="D2">
-        <v>56.93</v>
+        <v>56.929931640625</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
       <c r="F2">
-        <v>75.88</v>
+        <v>75.8798828125</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -590,7 +590,7 @@
         <v>15</v>
       </c>
       <c r="D3">
-        <v>103.39</v>
+        <v>103.39013671875</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
@@ -610,13 +610,13 @@
         <v>16</v>
       </c>
       <c r="D4">
-        <v>59.61</v>
+        <v>59.610107421875</v>
       </c>
       <c r="E4" t="s">
         <v>12</v>
       </c>
       <c r="F4">
-        <v>66.58</v>
+        <v>66.580078125</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -630,13 +630,13 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>74.28</v>
+        <v>74.27978515625</v>
       </c>
       <c r="E5" t="s">
         <v>13</v>
       </c>
       <c r="F5">
-        <v>88.68000000000001</v>
+        <v>88.68017578125</v>
       </c>
     </row>
   </sheetData>
